--- a/E/BEV03S.xlsx
+++ b/E/BEV03S.xlsx
@@ -622,6 +622,201 @@
     <t>STRWAY SOYA BEAN 310</t>
   </si>
   <si>
+    <t>10003389</t>
+  </si>
+  <si>
+    <t>KIRANTI SEHAT BLN150</t>
+  </si>
+  <si>
+    <t>20029054</t>
+  </si>
+  <si>
+    <t>KIRANTI JUICE 150ML</t>
+  </si>
+  <si>
+    <t>20137228</t>
+  </si>
+  <si>
+    <t>KIRANTI LYCHEE 150ML</t>
+  </si>
+  <si>
+    <t>20137229</t>
+  </si>
+  <si>
+    <t>KIRANTI BERRY 150ML</t>
+  </si>
+  <si>
+    <t>20140068</t>
+  </si>
+  <si>
+    <t>LARISST JELY LECI135</t>
+  </si>
+  <si>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20140066</t>
+  </si>
+  <si>
+    <t>LARISST JELY MANG135</t>
+  </si>
+  <si>
+    <t>20140067</t>
+  </si>
+  <si>
+    <t>LARISST JELY STRW135</t>
+  </si>
+  <si>
+    <t>20113377</t>
+  </si>
+  <si>
+    <t>FLRDINA COCO BIT 350</t>
+  </si>
+  <si>
+    <t>20043877</t>
+  </si>
+  <si>
+    <t>FLORIDINA ORANGE 350</t>
+  </si>
+  <si>
+    <t>20125638</t>
+  </si>
+  <si>
+    <t>NTRSARI JRK PRS 10'S</t>
+  </si>
+  <si>
+    <t>20026226</t>
+  </si>
+  <si>
+    <t>ULTRA TEH KOTAK 500</t>
+  </si>
+  <si>
+    <t>10036640</t>
+  </si>
+  <si>
+    <t>TEH KOTAK JASMINE300</t>
+  </si>
+  <si>
+    <t>20048435</t>
+  </si>
+  <si>
+    <t>TEH KOTAK LESS/S 300</t>
+  </si>
+  <si>
+    <t>20044334</t>
+  </si>
+  <si>
+    <t>SOSRO TEH BTL TPK300</t>
+  </si>
+  <si>
+    <t>10005128</t>
+  </si>
+  <si>
+    <t>SOSRO TEH KOTAK B250</t>
+  </si>
+  <si>
+    <t>20001119</t>
+  </si>
+  <si>
+    <t>SOSRO TEH KOTAK 4+2S</t>
+  </si>
+  <si>
+    <t>20114495</t>
+  </si>
+  <si>
+    <t>NESCAFE CPUCCINO 220</t>
+  </si>
+  <si>
+    <t>20114493</t>
+  </si>
+  <si>
+    <t>NESCAFE LATTE 220ML</t>
+  </si>
+  <si>
+    <t>20121456</t>
+  </si>
+  <si>
+    <t>NSCAFE ICE BLACK 220</t>
+  </si>
+  <si>
+    <t>20123322</t>
+  </si>
+  <si>
+    <t>GOLDA CAPPUCCINO 200</t>
+  </si>
+  <si>
+    <t>20087542</t>
+  </si>
+  <si>
+    <t>GOLDA COFF.DOLCE 200</t>
+  </si>
+  <si>
+    <t>20102789</t>
+  </si>
+  <si>
+    <t>ABC CHOCMLT COFF 180</t>
+  </si>
+  <si>
+    <t>20102790</t>
+  </si>
+  <si>
+    <t>ABC MILK COFFEE 180</t>
+  </si>
+  <si>
+    <t>20036157</t>
+  </si>
+  <si>
+    <t>SOSRO TEH BOTOL 450</t>
+  </si>
+  <si>
+    <t>20037565</t>
+  </si>
+  <si>
+    <t>PUCUK/H TEH MLATI500</t>
+  </si>
+  <si>
+    <t>20048155</t>
+  </si>
+  <si>
+    <t>PUCUK/H TEH L/SGR350</t>
+  </si>
+  <si>
+    <t>20035484</t>
+  </si>
+  <si>
+    <t>PUCUK/H TEH MLATI350</t>
+  </si>
+  <si>
+    <t>20072249</t>
+  </si>
+  <si>
+    <t>SOSRO TEH BOTOL 350</t>
+  </si>
+  <si>
+    <t>20066455</t>
+  </si>
+  <si>
+    <t>FRUIT TEA APPLE 350</t>
+  </si>
+  <si>
+    <t>20066454</t>
+  </si>
+  <si>
+    <t>FRUIT TEA BLCKCR 350</t>
+  </si>
+  <si>
+    <t>20073495</t>
+  </si>
+  <si>
+    <t>FRUIT TEA FREEZE 350</t>
+  </si>
+  <si>
+    <t>20101897</t>
+  </si>
+  <si>
+    <t>IDM TEH APEL 350ML</t>
+  </si>
+  <si>
     <t>20139297</t>
   </si>
   <si>
@@ -632,201 +827,6 @@
   </si>
   <si>
     <t>POP ICE MANGO 5'S</t>
-  </si>
-  <si>
-    <t>20140068</t>
-  </si>
-  <si>
-    <t>LARISST JELY LECI135</t>
-  </si>
-  <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20140066</t>
-  </si>
-  <si>
-    <t>LARISST JELY MANG135</t>
-  </si>
-  <si>
-    <t>20140067</t>
-  </si>
-  <si>
-    <t>LARISST JELY STRW135</t>
-  </si>
-  <si>
-    <t>10003389</t>
-  </si>
-  <si>
-    <t>KIRANTI SEHAT BLN150</t>
-  </si>
-  <si>
-    <t>20029054</t>
-  </si>
-  <si>
-    <t>KIRANTI JUICE 150ML</t>
-  </si>
-  <si>
-    <t>20137228</t>
-  </si>
-  <si>
-    <t>KIRANTI LYCHEE 150ML</t>
-  </si>
-  <si>
-    <t>20137229</t>
-  </si>
-  <si>
-    <t>KIRANTI BERRY 150ML</t>
-  </si>
-  <si>
-    <t>20125638</t>
-  </si>
-  <si>
-    <t>NTRSARI JRK PRS 10'S</t>
-  </si>
-  <si>
-    <t>20113377</t>
-  </si>
-  <si>
-    <t>FLRDINA COCO BIT 350</t>
-  </si>
-  <si>
-    <t>20043877</t>
-  </si>
-  <si>
-    <t>FLORIDINA ORANGE 350</t>
-  </si>
-  <si>
-    <t>20026226</t>
-  </si>
-  <si>
-    <t>ULTRA TEH KOTAK 500</t>
-  </si>
-  <si>
-    <t>10036640</t>
-  </si>
-  <si>
-    <t>TEH KOTAK JASMINE300</t>
-  </si>
-  <si>
-    <t>20048435</t>
-  </si>
-  <si>
-    <t>TEH KOTAK LESS/S 300</t>
-  </si>
-  <si>
-    <t>20044334</t>
-  </si>
-  <si>
-    <t>SOSRO TEH BTL TPK300</t>
-  </si>
-  <si>
-    <t>10005128</t>
-  </si>
-  <si>
-    <t>SOSRO TEH KOTAK B250</t>
-  </si>
-  <si>
-    <t>20001119</t>
-  </si>
-  <si>
-    <t>SOSRO TEH KOTAK 4+2S</t>
-  </si>
-  <si>
-    <t>20114495</t>
-  </si>
-  <si>
-    <t>NESCAFE CPUCCINO 220</t>
-  </si>
-  <si>
-    <t>20114493</t>
-  </si>
-  <si>
-    <t>NESCAFE LATTE 220ML</t>
-  </si>
-  <si>
-    <t>20121456</t>
-  </si>
-  <si>
-    <t>NSCAFE ICE BLACK 220</t>
-  </si>
-  <si>
-    <t>20123322</t>
-  </si>
-  <si>
-    <t>GOLDA CAPPUCCINO 200</t>
-  </si>
-  <si>
-    <t>20087542</t>
-  </si>
-  <si>
-    <t>GOLDA COFF.DOLCE 200</t>
-  </si>
-  <si>
-    <t>20102789</t>
-  </si>
-  <si>
-    <t>ABC CHOCMLT COFF 180</t>
-  </si>
-  <si>
-    <t>20102790</t>
-  </si>
-  <si>
-    <t>ABC MILK COFFEE 180</t>
-  </si>
-  <si>
-    <t>20036157</t>
-  </si>
-  <si>
-    <t>SOSRO TEH BOTOL 450</t>
-  </si>
-  <si>
-    <t>20037565</t>
-  </si>
-  <si>
-    <t>PUCUK/H TEH MLATI500</t>
-  </si>
-  <si>
-    <t>20048155</t>
-  </si>
-  <si>
-    <t>PUCUK/H TEH L/SGR350</t>
-  </si>
-  <si>
-    <t>20035484</t>
-  </si>
-  <si>
-    <t>PUCUK/H TEH MLATI350</t>
-  </si>
-  <si>
-    <t>20072249</t>
-  </si>
-  <si>
-    <t>SOSRO TEH BOTOL 350</t>
-  </si>
-  <si>
-    <t>20066455</t>
-  </si>
-  <si>
-    <t>FRUIT TEA APPLE 350</t>
-  </si>
-  <si>
-    <t>20066454</t>
-  </si>
-  <si>
-    <t>FRUIT TEA BLCKCR 350</t>
-  </si>
-  <si>
-    <t>20073495</t>
-  </si>
-  <si>
-    <t>FRUIT TEA FREEZE 350</t>
-  </si>
-  <si>
-    <t>20101897</t>
-  </si>
-  <si>
-    <t>IDM TEH APEL 350ML</t>
   </si>
   <si>
     <t>20015838</t>
@@ -3534,15 +3534,15 @@
         <v>18</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>209</v>
+        <v>34</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="B96" s="1" t="s">
         <v>210</v>
-      </c>
-      <c r="B96" s="1" t="s">
-        <v>211</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>3</v>
@@ -3554,15 +3554,15 @@
         <v>21</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>209</v>
+        <v>34</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="B97" s="1" t="s">
         <v>212</v>
-      </c>
-      <c r="B97" s="1" t="s">
-        <v>213</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>3</v>
@@ -3574,7 +3574,7 @@
         <v>24</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
@@ -3594,7 +3594,7 @@
         <v>27</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>34</v>
+        <v>213</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
@@ -3614,7 +3614,7 @@
         <v>30</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>34</v>
+        <v>213</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
@@ -3631,7 +3631,7 @@
         <v>33</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>34</v>
@@ -3651,7 +3651,7 @@
         <v>33</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>34</v>
@@ -3671,7 +3671,7 @@
         <v>33</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>34</v>
@@ -3688,10 +3688,10 @@
         <v>3</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>73</v>
+        <v>4</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>34</v>
@@ -3708,10 +3708,10 @@
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>142</v>
+        <v>8</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>34</v>
@@ -3731,7 +3731,7 @@
         <v>37</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>34</v>
@@ -3751,7 +3751,7 @@
         <v>37</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>34</v>
@@ -3771,7 +3771,7 @@
         <v>37</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>34</v>
@@ -3791,7 +3791,7 @@
         <v>37</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>34</v>
@@ -3811,10 +3811,10 @@
         <v>37</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>34</v>
+        <v>109</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
@@ -3831,10 +3831,10 @@
         <v>37</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>34</v>
+        <v>109</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
@@ -3851,7 +3851,7 @@
         <v>37</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>109</v>
@@ -3871,10 +3871,10 @@
         <v>37</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>109</v>
+        <v>34</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
@@ -3891,10 +3891,10 @@
         <v>37</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>109</v>
+        <v>34</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
@@ -3911,10 +3911,10 @@
         <v>37</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>33</v>
+        <v>70</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>34</v>
+        <v>5</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
@@ -3931,10 +3931,10 @@
         <v>37</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>37</v>
+        <v>73</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>34</v>
+        <v>5</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
@@ -3948,13 +3948,13 @@
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>70</v>
+        <v>4</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>5</v>
+        <v>34</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
@@ -3968,13 +3968,13 @@
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>73</v>
+        <v>8</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>5</v>
+        <v>34</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
@@ -3991,7 +3991,7 @@
         <v>70</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>34</v>
@@ -4011,7 +4011,7 @@
         <v>70</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>34</v>
@@ -4031,7 +4031,7 @@
         <v>70</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>34</v>
@@ -4051,7 +4051,7 @@
         <v>70</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>34</v>
@@ -4071,7 +4071,7 @@
         <v>70</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>34</v>
@@ -4091,7 +4091,7 @@
         <v>70</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>34</v>
@@ -4111,10 +4111,10 @@
         <v>70</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>34</v>
+        <v>213</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
@@ -4131,7 +4131,7 @@
         <v>70</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>34</v>
@@ -4151,10 +4151,10 @@
         <v>70</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>209</v>
+        <v>34</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
@@ -4314,7 +4314,7 @@
         <v>27</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
@@ -4994,7 +4994,7 @@
         <v>21</v>
       </c>
       <c r="F168" s="1" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
@@ -5154,7 +5154,7 @@
         <v>8</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">

--- a/E/BEV03S.xlsx
+++ b/E/BEV03S.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1128" uniqueCount="408">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1134" uniqueCount="410">
   <si>
     <t/>
   </si>
@@ -211,12 +211,6 @@
     <t>INDOMLK KID F.CRM115</t>
   </si>
   <si>
-    <t>20136817</t>
-  </si>
-  <si>
-    <t>INDOMLK KID BNANA115</t>
-  </si>
-  <si>
     <t>20112746</t>
   </si>
   <si>
@@ -310,10 +304,16 @@
     <t>DANCOW FRTGO VNLA110</t>
   </si>
   <si>
+    <t>14</t>
+  </si>
+  <si>
     <t>20057229</t>
   </si>
   <si>
-    <t>VIDORAN SUSU COK 110</t>
+    <t>VIDRN XMRT SS COK110</t>
+  </si>
+  <si>
+    <t>15</t>
   </si>
   <si>
     <t>20113180</t>
@@ -328,27 +328,36 @@
     <t>MILO ACT-GO 4X180ML</t>
   </si>
   <si>
+    <t>20143400</t>
+  </si>
+  <si>
+    <t>MILO DRNK EXT CHO3+1</t>
+  </si>
+  <si>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20087290</t>
+  </si>
+  <si>
+    <t>HILO SCHL UHT CHO200</t>
+  </si>
+  <si>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20134048</t>
+  </si>
+  <si>
+    <t>HILO PRTEIN CHOCO190</t>
+  </si>
+  <si>
     <t>20130034</t>
   </si>
   <si>
     <t>OATSDE STR BR.BLN200</t>
   </si>
   <si>
-    <t>20087290</t>
-  </si>
-  <si>
-    <t>HILO SCHL UHT CHO200</t>
-  </si>
-  <si>
-    <t>RT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20134048</t>
-  </si>
-  <si>
-    <t>HILO PRTEIN CHOCO190</t>
-  </si>
-  <si>
     <t>20053799</t>
   </si>
   <si>
@@ -439,9 +448,6 @@
     <t>BEAR BRAND STERIL189</t>
   </si>
   <si>
-    <t>14</t>
-  </si>
-  <si>
     <t>20133540</t>
   </si>
   <si>
@@ -652,9 +658,6 @@
     <t>LARISST JELY LECI135</t>
   </si>
   <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
     <t>20140066</t>
   </si>
   <si>
@@ -667,6 +670,12 @@
     <t>LARISST JELY STRW135</t>
   </si>
   <si>
+    <t>20143385</t>
+  </si>
+  <si>
+    <t>SUNPRIDE MGOGVA2X220</t>
+  </si>
+  <si>
     <t>20113377</t>
   </si>
   <si>
@@ -998,9 +1007,6 @@
   </si>
   <si>
     <t>BUAVITA ORANGE 1L</t>
-  </si>
-  <si>
-    <t>15</t>
   </si>
   <si>
     <t>20067201</t>
@@ -1627,7 +1633,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F188"/>
+  <dimension ref="A1:F189"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -2171,7 +2177,7 @@
         <v>11</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>37</v>
+        <v>68</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>34</v>
@@ -2179,10 +2185,10 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>3</v>
@@ -2191,7 +2197,7 @@
         <v>11</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>34</v>
@@ -2199,30 +2205,30 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D29" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E29" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E29" s="1" t="s">
-        <v>73</v>
-      </c>
       <c r="F29" s="1" t="s">
-        <v>34</v>
+        <v>74</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>3</v>
@@ -2231,10 +2237,10 @@
         <v>15</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>76</v>
+        <v>34</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -2251,7 +2257,7 @@
         <v>15</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>34</v>
@@ -2271,7 +2277,7 @@
         <v>15</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>34</v>
@@ -2291,7 +2297,7 @@
         <v>15</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>34</v>
@@ -2311,7 +2317,7 @@
         <v>15</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>34</v>
@@ -2331,7 +2337,7 @@
         <v>15</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>34</v>
@@ -2351,7 +2357,7 @@
         <v>15</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>34</v>
@@ -2371,7 +2377,7 @@
         <v>15</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>34</v>
@@ -2391,7 +2397,7 @@
         <v>15</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>30</v>
+        <v>68</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>34</v>
@@ -2411,7 +2417,7 @@
         <v>15</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>33</v>
+        <v>71</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>34</v>
@@ -2431,7 +2437,7 @@
         <v>15</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>37</v>
+        <v>97</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>34</v>
@@ -2439,10 +2445,10 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>3</v>
@@ -2451,38 +2457,38 @@
         <v>15</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>73</v>
+        <v>4</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>3</v>
@@ -2491,7 +2497,7 @@
         <v>18</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>34</v>
@@ -2499,10 +2505,10 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>3</v>
@@ -2511,18 +2517,18 @@
         <v>18</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>34</v>
+        <v>107</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>3</v>
@@ -2531,18 +2537,18 @@
         <v>18</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>34</v>
+        <v>110</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>3</v>
@@ -2551,18 +2557,18 @@
         <v>18</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>109</v>
+        <v>34</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>3</v>
@@ -2571,7 +2577,7 @@
         <v>18</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>34</v>
@@ -2579,10 +2585,10 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>3</v>
@@ -2591,7 +2597,7 @@
         <v>18</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>34</v>
@@ -2599,10 +2605,10 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>3</v>
@@ -2611,7 +2617,7 @@
         <v>18</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>34</v>
@@ -2619,10 +2625,10 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>3</v>
@@ -2639,10 +2645,10 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>3</v>
@@ -2659,10 +2665,10 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>3</v>
@@ -2679,10 +2685,10 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>3</v>
@@ -2699,10 +2705,10 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>3</v>
@@ -2719,10 +2725,10 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>3</v>
@@ -2739,10 +2745,10 @@
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>3</v>
@@ -2759,10 +2765,10 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>3</v>
@@ -2779,10 +2785,10 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>3</v>
@@ -2799,10 +2805,10 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>3</v>
@@ -2819,10 +2825,10 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>3</v>
@@ -2839,10 +2845,10 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>3</v>
@@ -2851,7 +2857,7 @@
         <v>21</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>34</v>
@@ -2859,10 +2865,10 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>3</v>
@@ -2871,7 +2877,7 @@
         <v>21</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>142</v>
+        <v>97</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>34</v>
@@ -2879,10 +2885,10 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>3</v>
@@ -2899,10 +2905,10 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>3</v>
@@ -2919,10 +2925,10 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>3</v>
@@ -2939,10 +2945,10 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>3</v>
@@ -2959,10 +2965,10 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>3</v>
@@ -2979,10 +2985,10 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>3</v>
@@ -2999,10 +3005,10 @@
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>3</v>
@@ -3019,10 +3025,10 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>3</v>
@@ -3039,10 +3045,10 @@
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>3</v>
@@ -3059,10 +3065,10 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>3</v>
@@ -3079,10 +3085,10 @@
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>3</v>
@@ -3099,10 +3105,10 @@
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>3</v>
@@ -3119,10 +3125,10 @@
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>3</v>
@@ -3139,10 +3145,10 @@
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>3</v>
@@ -3159,10 +3165,10 @@
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>3</v>
@@ -3179,10 +3185,10 @@
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>3</v>
@@ -3199,10 +3205,10 @@
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>3</v>
@@ -3219,10 +3225,10 @@
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>3</v>
@@ -3239,10 +3245,10 @@
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>3</v>
@@ -3259,10 +3265,10 @@
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>3</v>
@@ -3279,10 +3285,10 @@
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>3</v>
@@ -3299,10 +3305,10 @@
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>3</v>
@@ -3314,15 +3320,15 @@
         <v>11</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>3</v>
@@ -3334,15 +3340,15 @@
         <v>15</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>3</v>
@@ -3359,10 +3365,10 @@
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>3</v>
@@ -3379,10 +3385,10 @@
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>3</v>
@@ -3399,10 +3405,10 @@
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>3</v>
@@ -3419,10 +3425,10 @@
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>3</v>
@@ -3439,10 +3445,10 @@
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>3</v>
@@ -3459,10 +3465,10 @@
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>3</v>
@@ -3479,10 +3485,10 @@
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>3</v>
@@ -3499,10 +3505,10 @@
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>3</v>
@@ -3519,10 +3525,10 @@
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>3</v>
@@ -3539,10 +3545,10 @@
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>3</v>
@@ -3559,10 +3565,10 @@
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>3</v>
@@ -3574,15 +3580,15 @@
         <v>24</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>213</v>
+        <v>107</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>3</v>
@@ -3594,15 +3600,15 @@
         <v>27</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>213</v>
+        <v>107</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>3</v>
@@ -3614,15 +3620,15 @@
         <v>30</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>213</v>
+        <v>107</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>3</v>
@@ -3631,7 +3637,7 @@
         <v>33</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>34</v>
@@ -3639,10 +3645,10 @@
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>3</v>
@@ -3651,7 +3657,7 @@
         <v>33</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>70</v>
+        <v>37</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>34</v>
@@ -3659,10 +3665,10 @@
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>3</v>
@@ -3671,7 +3677,7 @@
         <v>33</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>34</v>
@@ -3679,19 +3685,19 @@
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C103" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>4</v>
+        <v>71</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>34</v>
@@ -3699,10 +3705,10 @@
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>3</v>
@@ -3711,7 +3717,7 @@
         <v>37</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>34</v>
@@ -3719,10 +3725,10 @@
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C105" s="1" t="s">
         <v>3</v>
@@ -3731,7 +3737,7 @@
         <v>37</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>34</v>
@@ -3739,10 +3745,10 @@
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>3</v>
@@ -3751,7 +3757,7 @@
         <v>37</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>34</v>
@@ -3759,10 +3765,10 @@
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>3</v>
@@ -3771,7 +3777,7 @@
         <v>37</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>34</v>
@@ -3779,10 +3785,10 @@
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>3</v>
@@ -3791,7 +3797,7 @@
         <v>37</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>34</v>
@@ -3799,10 +3805,10 @@
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C109" s="1" t="s">
         <v>3</v>
@@ -3811,18 +3817,18 @@
         <v>37</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>109</v>
+        <v>34</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>3</v>
@@ -3831,18 +3837,18 @@
         <v>37</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>3</v>
@@ -3851,18 +3857,18 @@
         <v>37</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>3</v>
@@ -3871,18 +3877,18 @@
         <v>37</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>34</v>
+        <v>110</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>3</v>
@@ -3891,7 +3897,7 @@
         <v>37</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>34</v>
@@ -3899,10 +3905,10 @@
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>3</v>
@@ -3911,18 +3917,18 @@
         <v>37</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>70</v>
+        <v>37</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>5</v>
+        <v>34</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>3</v>
@@ -3931,7 +3937,7 @@
         <v>37</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>5</v>
@@ -3939,39 +3945,39 @@
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>70</v>
+        <v>37</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>4</v>
+        <v>71</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>34</v>
+        <v>5</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>34</v>
@@ -3979,19 +3985,19 @@
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>34</v>
@@ -3999,19 +4005,19 @@
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>34</v>
@@ -4019,19 +4025,19 @@
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>34</v>
@@ -4039,19 +4045,19 @@
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>34</v>
@@ -4059,19 +4065,19 @@
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>34</v>
@@ -4079,19 +4085,19 @@
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C123" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>34</v>
@@ -4099,59 +4105,59 @@
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C124" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>213</v>
+        <v>34</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>34</v>
+        <v>107</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C126" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>34</v>
@@ -4159,79 +4165,79 @@
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C127" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>4</v>
+        <v>37</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>109</v>
+        <v>34</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C128" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C129" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>34</v>
+        <v>110</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C130" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F130" s="1" t="s">
         <v>34</v>
@@ -4239,19 +4245,19 @@
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C131" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F131" s="1" t="s">
         <v>34</v>
@@ -4259,99 +4265,99 @@
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C132" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>109</v>
+        <v>34</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C133" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C134" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>213</v>
+        <v>110</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C135" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>34</v>
+        <v>107</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C136" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>34</v>
@@ -4359,19 +4365,19 @@
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C137" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>70</v>
+        <v>37</v>
       </c>
       <c r="F137" s="1" t="s">
         <v>34</v>
@@ -4379,19 +4385,19 @@
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C138" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="F138" s="1" t="s">
         <v>34</v>
@@ -4399,19 +4405,19 @@
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C139" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>142</v>
+        <v>71</v>
       </c>
       <c r="F139" s="1" t="s">
         <v>34</v>
@@ -4419,59 +4425,59 @@
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C140" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>142</v>
+        <v>71</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>4</v>
+        <v>97</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>109</v>
+        <v>34</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C141" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>142</v>
+        <v>97</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>34</v>
+        <v>110</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C142" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>142</v>
+        <v>97</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F142" s="1" t="s">
         <v>34</v>
@@ -4479,39 +4485,39 @@
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C143" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>142</v>
+        <v>97</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C144" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>142</v>
+        <v>97</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F144" s="1" t="s">
         <v>12</v>
@@ -4519,19 +4525,19 @@
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C145" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>142</v>
+        <v>97</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F145" s="1" t="s">
         <v>12</v>
@@ -4539,19 +4545,19 @@
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C146" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>142</v>
+        <v>97</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F146" s="1" t="s">
         <v>12</v>
@@ -4559,39 +4565,39 @@
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C147" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>142</v>
+        <v>97</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C148" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>142</v>
+        <v>97</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F148" s="1" t="s">
         <v>5</v>
@@ -4599,19 +4605,19 @@
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C149" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>142</v>
+        <v>97</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F149" s="1" t="s">
         <v>5</v>
@@ -4619,19 +4625,19 @@
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C150" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>142</v>
+        <v>97</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="F150" s="1" t="s">
         <v>5</v>
@@ -4639,19 +4645,19 @@
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C151" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>142</v>
+        <v>97</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>70</v>
+        <v>37</v>
       </c>
       <c r="F151" s="1" t="s">
         <v>5</v>
@@ -4659,42 +4665,42 @@
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C152" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>142</v>
+        <v>97</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>76</v>
+        <v>5</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C153" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>142</v>
+        <v>97</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>142</v>
+        <v>71</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>326</v>
+        <v>74</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
@@ -4708,13 +4714,13 @@
         <v>3</v>
       </c>
       <c r="D154" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E154" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="F154" s="1" t="s">
         <v>329</v>
-      </c>
-      <c r="E154" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F154" s="1" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
@@ -4728,10 +4734,10 @@
         <v>3</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>329</v>
+        <v>100</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F155" s="1" t="s">
         <v>34</v>
@@ -4748,10 +4754,10 @@
         <v>3</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>329</v>
+        <v>100</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F156" s="1" t="s">
         <v>34</v>
@@ -4768,10 +4774,10 @@
         <v>3</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>329</v>
+        <v>100</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F157" s="1" t="s">
         <v>34</v>
@@ -4788,13 +4794,13 @@
         <v>3</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>329</v>
+        <v>100</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
@@ -4808,10 +4814,10 @@
         <v>3</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>329</v>
+        <v>100</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F159" s="1" t="s">
         <v>12</v>
@@ -4828,10 +4834,10 @@
         <v>3</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>329</v>
+        <v>100</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F160" s="1" t="s">
         <v>12</v>
@@ -4848,13 +4854,13 @@
         <v>3</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>329</v>
+        <v>100</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
@@ -4868,10 +4874,10 @@
         <v>3</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>329</v>
+        <v>100</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F162" s="1" t="s">
         <v>5</v>
@@ -4888,30 +4894,30 @@
         <v>3</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>348</v>
+        <v>100</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>34</v>
+        <v>5</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="B164" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="B164" s="1" t="s">
+      <c r="C164" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D164" s="1" t="s">
         <v>350</v>
       </c>
-      <c r="C164" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D164" s="1" t="s">
-        <v>348</v>
-      </c>
       <c r="E164" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F164" s="1" t="s">
         <v>34</v>
@@ -4928,10 +4934,10 @@
         <v>3</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F165" s="1" t="s">
         <v>34</v>
@@ -4948,10 +4954,10 @@
         <v>3</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F166" s="1" t="s">
         <v>34</v>
@@ -4968,10 +4974,10 @@
         <v>3</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F167" s="1" t="s">
         <v>34</v>
@@ -4988,13 +4994,13 @@
         <v>3</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F168" s="1" t="s">
-        <v>213</v>
+        <v>34</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
@@ -5008,33 +5014,33 @@
         <v>3</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>361</v>
+        <v>350</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>12</v>
+        <v>107</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="B170" s="1" t="s">
         <v>362</v>
       </c>
-      <c r="B170" s="1" t="s">
+      <c r="C170" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D170" s="1" t="s">
         <v>363</v>
       </c>
-      <c r="C170" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D170" s="1" t="s">
-        <v>361</v>
-      </c>
       <c r="E170" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
@@ -5048,33 +5054,33 @@
         <v>3</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>366</v>
+        <v>34</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="B172" s="1" t="s">
         <v>367</v>
       </c>
-      <c r="B172" s="1" t="s">
+      <c r="C172" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D172" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="E172" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F172" s="1" t="s">
         <v>368</v>
-      </c>
-      <c r="C172" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D172" s="1" t="s">
-        <v>361</v>
-      </c>
-      <c r="E172" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F172" s="1" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
@@ -5088,73 +5094,73 @@
         <v>3</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>371</v>
+        <v>363</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>34</v>
+        <v>110</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="B174" s="1" t="s">
         <v>372</v>
       </c>
-      <c r="B174" s="1" t="s">
+      <c r="C174" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D174" s="1" t="s">
         <v>373</v>
-      </c>
-      <c r="C174" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D174" s="1" t="s">
-        <v>374</v>
       </c>
       <c r="E174" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F174" s="1" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="B175" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="B175" s="1" t="s">
+      <c r="C175" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D175" s="1" t="s">
         <v>376</v>
-      </c>
-      <c r="C175" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D175" s="1" t="s">
-        <v>377</v>
       </c>
       <c r="E175" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="B176" s="1" t="s">
         <v>378</v>
       </c>
-      <c r="B176" s="1" t="s">
+      <c r="C176" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D176" s="1" t="s">
         <v>379</v>
       </c>
-      <c r="C176" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D176" s="1" t="s">
-        <v>377</v>
-      </c>
       <c r="E176" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>213</v>
+        <v>34</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
@@ -5168,13 +5174,13 @@
         <v>3</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>366</v>
+        <v>107</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
@@ -5188,13 +5194,13 @@
         <v>3</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>34</v>
+        <v>368</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
@@ -5208,10 +5214,10 @@
         <v>3</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F179" s="1" t="s">
         <v>34</v>
@@ -5228,93 +5234,93 @@
         <v>3</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>388</v>
+        <v>379</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="B181" s="1" t="s">
         <v>389</v>
       </c>
-      <c r="B181" s="1" t="s">
+      <c r="C181" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D181" s="1" t="s">
         <v>390</v>
       </c>
-      <c r="C181" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D181" s="1" t="s">
-        <v>388</v>
-      </c>
       <c r="E181" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F181" s="1" t="s">
-        <v>391</v>
+        <v>12</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="B182" s="1" t="s">
         <v>392</v>
       </c>
-      <c r="B182" s="1" t="s">
+      <c r="C182" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D182" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="E182" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F182" s="1" t="s">
         <v>393</v>
-      </c>
-      <c r="C182" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D182" s="1" t="s">
-        <v>388</v>
-      </c>
-      <c r="E182" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F182" s="1" t="s">
-        <v>394</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="B183" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="B183" s="1" t="s">
+      <c r="C183" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D183" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="E183" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F183" s="1" t="s">
         <v>396</v>
-      </c>
-      <c r="C183" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D183" s="1" t="s">
-        <v>388</v>
-      </c>
-      <c r="E183" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F183" s="1" t="s">
-        <v>397</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="B184" s="1" t="s">
         <v>398</v>
       </c>
-      <c r="B184" s="1" t="s">
+      <c r="C184" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D184" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="E184" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F184" s="1" t="s">
         <v>399</v>
-      </c>
-      <c r="C184" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D184" s="1" t="s">
-        <v>388</v>
-      </c>
-      <c r="E184" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F184" s="1" t="s">
-        <v>394</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
@@ -5328,13 +5334,13 @@
         <v>3</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F185" s="1" t="s">
-        <v>109</v>
+        <v>396</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
@@ -5348,13 +5354,13 @@
         <v>3</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F186" s="1" t="s">
-        <v>34</v>
+        <v>110</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
@@ -5368,13 +5374,13 @@
         <v>3</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F187" s="1" t="s">
-        <v>109</v>
+        <v>34</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
@@ -5388,12 +5394,32 @@
         <v>3</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="E188" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F188" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="189" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A189" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="B189" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="C189" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D189" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="E189" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="F188" s="1" t="s">
+      <c r="F189" s="1" t="s">
         <v>34</v>
       </c>
     </row>

--- a/E/BEV03S.xlsx
+++ b/E/BEV03S.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1134" uniqueCount="410">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1152" uniqueCount="416">
   <si>
     <t/>
   </si>
@@ -850,6 +850,30 @@
     <t>POCARI SWEAT 500ML</t>
   </si>
   <si>
+    <t>20142818</t>
+  </si>
+  <si>
+    <t>EWATER GRAPEFRT 555</t>
+  </si>
+  <si>
+    <t>20142819</t>
+  </si>
+  <si>
+    <t>EWATER LEMON 555ML</t>
+  </si>
+  <si>
+    <t>20142862</t>
+  </si>
+  <si>
+    <t>EWATER GRPFRT 380</t>
+  </si>
+  <si>
+    <t>20142863</t>
+  </si>
+  <si>
+    <t>EWATER LEMON 380</t>
+  </si>
+  <si>
     <t>20019674</t>
   </si>
   <si>
@@ -862,177 +886,171 @@
     <t>YOU C1000 LMN WTR500</t>
   </si>
   <si>
+    <t>20009737</t>
+  </si>
+  <si>
+    <t>YOU C1000 DRK ORG140</t>
+  </si>
+  <si>
+    <t>10039897</t>
+  </si>
+  <si>
+    <t>YOU C1000 DRK LMN140</t>
+  </si>
+  <si>
+    <t>20115636</t>
+  </si>
+  <si>
+    <t>YOU C1000 DRK MGO140</t>
+  </si>
+  <si>
+    <t>20002504</t>
+  </si>
+  <si>
+    <t>ADEM SARI BOX 5'S</t>
+  </si>
+  <si>
+    <t>20141508</t>
+  </si>
+  <si>
+    <t>KRTINGDAENG BDD3X150</t>
+  </si>
+  <si>
+    <t>20121348</t>
+  </si>
+  <si>
+    <t>LASEGAR TWST J-L 320</t>
+  </si>
+  <si>
+    <t>20040276</t>
+  </si>
+  <si>
+    <t>ADEM SARI CK KLG 320</t>
+  </si>
+  <si>
+    <t>20071642</t>
+  </si>
+  <si>
+    <t>ADEMSARI CK SPRK 320</t>
+  </si>
+  <si>
+    <t>10003627</t>
+  </si>
+  <si>
+    <t>C/B PENY.ORANGE320</t>
+  </si>
+  <si>
+    <t>10004237</t>
+  </si>
+  <si>
+    <t>C/B PENY.LECI 320ML</t>
+  </si>
+  <si>
+    <t>10003842</t>
+  </si>
+  <si>
+    <t>C/B PENY.JAMBU 320</t>
+  </si>
+  <si>
+    <t>10037437</t>
+  </si>
+  <si>
+    <t>C/B PENY.STRAW 320</t>
+  </si>
+  <si>
+    <t>20037150</t>
+  </si>
+  <si>
+    <t>KAKI3 PENY.JAMBU 320</t>
+  </si>
+  <si>
+    <t>20037144</t>
+  </si>
+  <si>
+    <t>KAKI3 PENY.LECI 320</t>
+  </si>
+  <si>
+    <t>20069199</t>
+  </si>
+  <si>
+    <t>KAKI3 LMN.LM KLG 320</t>
+  </si>
+  <si>
+    <t>20045995</t>
+  </si>
+  <si>
+    <t>KAKI3 ANAK STRO 238</t>
+  </si>
+  <si>
+    <t>20045996</t>
+  </si>
+  <si>
+    <t>KAKI3 ANAK LECI 238</t>
+  </si>
+  <si>
+    <t>20055226</t>
+  </si>
+  <si>
+    <t>NTRIVE/B  STRWBRY100</t>
+  </si>
+  <si>
+    <t>20082247</t>
+  </si>
+  <si>
+    <t>NTRVE BNCOL ORG 100</t>
+  </si>
+  <si>
+    <t>RT,(E-0.5B)</t>
+  </si>
+  <si>
+    <t>20115157</t>
+  </si>
+  <si>
+    <t>BUAVITA ORANGE 1L</t>
+  </si>
+  <si>
+    <t>20067201</t>
+  </si>
+  <si>
+    <t>BUAVITA MANGO TPK 1L</t>
+  </si>
+  <si>
+    <t>20067200</t>
+  </si>
+  <si>
+    <t>BUAVITA GUAVA TPK 1L</t>
+  </si>
+  <si>
+    <t>20116490</t>
+  </si>
+  <si>
+    <t>HYDRO COCO 1L</t>
+  </si>
+  <si>
+    <t>20057867</t>
+  </si>
+  <si>
+    <t>HYDRO COCO 500ML</t>
+  </si>
+  <si>
+    <t>20018435</t>
+  </si>
+  <si>
+    <t>HYDRO COCO 250ML</t>
+  </si>
+  <si>
+    <t>20115548</t>
+  </si>
+  <si>
+    <t>IDM COCONUT WTR 250</t>
+  </si>
+  <si>
     <t>20053540</t>
   </si>
   <si>
     <t>ADEM SARI CK BTL 350</t>
   </si>
   <si>
-    <t>20057867</t>
-  </si>
-  <si>
-    <t>HYDRO COCO 500ML</t>
-  </si>
-  <si>
-    <t>20018435</t>
-  </si>
-  <si>
-    <t>HYDRO COCO 250ML</t>
-  </si>
-  <si>
-    <t>20115548</t>
-  </si>
-  <si>
-    <t>IDM COCONUT WTR 250</t>
-  </si>
-  <si>
-    <t>20009737</t>
-  </si>
-  <si>
-    <t>YOU C1000 DRK ORG140</t>
-  </si>
-  <si>
-    <t>10039897</t>
-  </si>
-  <si>
-    <t>YOU C1000 DRK LMN140</t>
-  </si>
-  <si>
-    <t>20115636</t>
-  </si>
-  <si>
-    <t>YOU C1000 DRK MGO140</t>
-  </si>
-  <si>
-    <t>20002504</t>
-  </si>
-  <si>
-    <t>ADEM SARI BOX 5'S</t>
-  </si>
-  <si>
-    <t>20141508</t>
-  </si>
-  <si>
-    <t>KRTINGDAENG BDD3X150</t>
-  </si>
-  <si>
-    <t>20121348</t>
-  </si>
-  <si>
-    <t>LASEGAR TWST J-L 320</t>
-  </si>
-  <si>
-    <t>20040276</t>
-  </si>
-  <si>
-    <t>ADEM SARI CK KLG 320</t>
-  </si>
-  <si>
-    <t>20071642</t>
-  </si>
-  <si>
-    <t>ADEMSARI CK SPRK 320</t>
-  </si>
-  <si>
-    <t>10003627</t>
-  </si>
-  <si>
-    <t>C/B PENY.ORANGE320</t>
-  </si>
-  <si>
-    <t>10004237</t>
-  </si>
-  <si>
-    <t>C/B PENY.LECI 320ML</t>
-  </si>
-  <si>
-    <t>10003842</t>
-  </si>
-  <si>
-    <t>C/B PENY.JAMBU 320</t>
-  </si>
-  <si>
-    <t>10037437</t>
-  </si>
-  <si>
-    <t>C/B PENY.STRAW 320</t>
-  </si>
-  <si>
-    <t>20037150</t>
-  </si>
-  <si>
-    <t>KAKI3 PENY.JAMBU 320</t>
-  </si>
-  <si>
-    <t>20037144</t>
-  </si>
-  <si>
-    <t>KAKI3 PENY.LECI 320</t>
-  </si>
-  <si>
-    <t>20069199</t>
-  </si>
-  <si>
-    <t>KAKI3 LMN.LM KLG 320</t>
-  </si>
-  <si>
-    <t>20045995</t>
-  </si>
-  <si>
-    <t>KAKI3 ANAK STRO 238</t>
-  </si>
-  <si>
-    <t>20045996</t>
-  </si>
-  <si>
-    <t>KAKI3 ANAK LECI 238</t>
-  </si>
-  <si>
-    <t>20055226</t>
-  </si>
-  <si>
-    <t>NTRIVE/B  STRWBRY100</t>
-  </si>
-  <si>
-    <t>20082247</t>
-  </si>
-  <si>
-    <t>NTRVE BNCOL ORG 100</t>
-  </si>
-  <si>
-    <t>RT,(E-0.5B)</t>
-  </si>
-  <si>
-    <t>20115157</t>
-  </si>
-  <si>
-    <t>BUAVITA ORANGE 1L</t>
-  </si>
-  <si>
-    <t>20067201</t>
-  </si>
-  <si>
-    <t>BUAVITA MANGO TPK 1L</t>
-  </si>
-  <si>
-    <t>20067200</t>
-  </si>
-  <si>
-    <t>BUAVITA GUAVA TPK 1L</t>
-  </si>
-  <si>
-    <t>20116490</t>
-  </si>
-  <si>
-    <t>HYDRO COCO 1L</t>
-  </si>
-  <si>
-    <t>20127835</t>
-  </si>
-  <si>
-    <t>ALANG SARI JN 300ML</t>
-  </si>
-  <si>
     <t>20130801</t>
   </si>
   <si>
@@ -1045,147 +1063,165 @@
     <t>C/BDK PENYEGAR 500ML</t>
   </si>
   <si>
+    <t>20099547</t>
+  </si>
+  <si>
+    <t>CRYSTALIN BTL 1500</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>20005530</t>
+  </si>
+  <si>
+    <t>NESTLE PURE LIFE 1.5</t>
+  </si>
+  <si>
+    <t>20137992</t>
+  </si>
+  <si>
+    <t>AQUVIVA BTL 1600ML</t>
+  </si>
+  <si>
+    <t>20139457</t>
+  </si>
+  <si>
+    <t>AQUVIVA 12X250ML</t>
+  </si>
+  <si>
+    <t>20126648</t>
+  </si>
+  <si>
+    <t>LE MINERALE 6X330ML</t>
+  </si>
+  <si>
+    <t>20094171</t>
+  </si>
+  <si>
+    <t>INDOMARET AIR 24X200</t>
+  </si>
+  <si>
+    <t>10000426</t>
+  </si>
+  <si>
+    <t>AQUA AIR MINERAL1500</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>20085988</t>
+  </si>
+  <si>
+    <t>LE MINERALE 1500ML</t>
+  </si>
+  <si>
+    <t>10004337</t>
+  </si>
+  <si>
+    <t>INDOMARET AIR/MN1500</t>
+  </si>
+  <si>
+    <t>PT,(E-1H)</t>
+  </si>
+  <si>
+    <t>20008785</t>
+  </si>
+  <si>
+    <t>CLUB AIR MNRL 1500ML</t>
+  </si>
+  <si>
+    <t>20069208</t>
+  </si>
+  <si>
+    <t>LE MINERALE 600ML</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>20090527</t>
+  </si>
+  <si>
+    <t>CRYSTALIN BTL 600mL</t>
+  </si>
+  <si>
+    <t>10003814</t>
+  </si>
+  <si>
+    <t>AQUA AIR MINERAL 600</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>20137991</t>
+  </si>
+  <si>
+    <t>AQUVIVA BTL 700ML</t>
+  </si>
+  <si>
+    <t>20141623</t>
+  </si>
+  <si>
+    <t>IDM AIR BDD 6X500ML</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>20142495</t>
+  </si>
+  <si>
+    <t>INDOMARET AIR MIN 1L</t>
+  </si>
+  <si>
+    <t>10004336</t>
+  </si>
+  <si>
+    <t>INDOMARET AIR MIN600</t>
+  </si>
+  <si>
+    <t>20005529</t>
+  </si>
+  <si>
+    <t>NESTLE PURE LIFE 600</t>
+  </si>
+  <si>
+    <t>20037131</t>
+  </si>
+  <si>
+    <t>PRIM-A AIR MNRAL 600</t>
+  </si>
+  <si>
+    <t>20008767</t>
+  </si>
+  <si>
+    <t>CLUB AIR MNRAL 600ML</t>
+  </si>
+  <si>
     <t>20134246</t>
   </si>
   <si>
     <t>KAKI3 PENYEGAR 350ML</t>
   </si>
   <si>
+    <t>21</t>
+  </si>
+  <si>
     <t>20037153</t>
   </si>
   <si>
     <t>KAKI3 PENYEGAR 500ML</t>
   </si>
   <si>
-    <t>20099547</t>
-  </si>
-  <si>
-    <t>CRYSTALIN BTL 1500</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>20005530</t>
-  </si>
-  <si>
-    <t>NESTLE PURE LIFE 1.5</t>
-  </si>
-  <si>
-    <t>20137992</t>
-  </si>
-  <si>
-    <t>AQUVIVA BTL 1600ML</t>
-  </si>
-  <si>
-    <t>20139457</t>
-  </si>
-  <si>
-    <t>AQUVIVA 12X250ML</t>
-  </si>
-  <si>
-    <t>20126648</t>
-  </si>
-  <si>
-    <t>LE MINERALE 6X330ML</t>
-  </si>
-  <si>
-    <t>20094171</t>
-  </si>
-  <si>
-    <t>INDOMARET AIR 24X200</t>
-  </si>
-  <si>
-    <t>10000426</t>
-  </si>
-  <si>
-    <t>AQUA AIR MINERAL1500</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>20085988</t>
-  </si>
-  <si>
-    <t>LE MINERALE 1500ML</t>
-  </si>
-  <si>
-    <t>10004337</t>
-  </si>
-  <si>
-    <t>INDOMARET AIR/MN1500</t>
-  </si>
-  <si>
-    <t>PT,(E-1H)</t>
-  </si>
-  <si>
-    <t>20008785</t>
-  </si>
-  <si>
-    <t>CLUB AIR MNRL 1500ML</t>
-  </si>
-  <si>
-    <t>20069208</t>
-  </si>
-  <si>
-    <t>LE MINERALE 600ML</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>10003814</t>
-  </si>
-  <si>
-    <t>AQUA AIR MINERAL 600</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>20141623</t>
-  </si>
-  <si>
-    <t>IDM AIR BDD 6X500ML</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>20142495</t>
-  </si>
-  <si>
-    <t>INDOMARET AIR MIN 1L</t>
-  </si>
-  <si>
-    <t>10004336</t>
-  </si>
-  <si>
-    <t>INDOMARET AIR MIN600</t>
-  </si>
-  <si>
-    <t>20137991</t>
-  </si>
-  <si>
-    <t>AQUVIVA BTL 700ML</t>
-  </si>
-  <si>
-    <t>20090527</t>
-  </si>
-  <si>
-    <t>CRYSTALIN BTL 600mL</t>
-  </si>
-  <si>
     <t>10015532</t>
   </si>
   <si>
     <t>AQUA AIR MINERAL 330</t>
   </si>
   <si>
-    <t>21</t>
-  </si>
-  <si>
     <t>20045052</t>
   </si>
   <si>
@@ -1223,24 +1259,6 @@
   </si>
   <si>
     <t>PRISTINE 8.6+ BTL600</t>
-  </si>
-  <si>
-    <t>20037131</t>
-  </si>
-  <si>
-    <t>PRIM-A AIR MNRAL 600</t>
-  </si>
-  <si>
-    <t>20008767</t>
-  </si>
-  <si>
-    <t>CLUB AIR MNRAL 600ML</t>
-  </si>
-  <si>
-    <t>20005529</t>
-  </si>
-  <si>
-    <t>NESTLE PURE LIFE 600</t>
   </si>
 </sst>
 </file>
@@ -1633,7 +1651,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F189"/>
+  <dimension ref="A1:F192"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -4300,7 +4318,7 @@
         <v>21</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>110</v>
+        <v>34</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
@@ -4320,7 +4338,7 @@
         <v>24</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>110</v>
+        <v>34</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
@@ -4340,7 +4358,7 @@
         <v>27</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>107</v>
+        <v>34</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
@@ -4357,7 +4375,7 @@
         <v>71</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>34</v>
@@ -4377,7 +4395,7 @@
         <v>71</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="F137" s="1" t="s">
         <v>34</v>
@@ -4397,7 +4415,7 @@
         <v>71</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>68</v>
+        <v>37</v>
       </c>
       <c r="F138" s="1" t="s">
         <v>34</v>
@@ -4417,7 +4435,7 @@
         <v>71</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="F139" s="1" t="s">
         <v>34</v>
@@ -4437,7 +4455,7 @@
         <v>71</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>97</v>
+        <v>71</v>
       </c>
       <c r="F140" s="1" t="s">
         <v>34</v>
@@ -4820,7 +4838,7 @@
         <v>18</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>12</v>
+        <v>110</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
@@ -4840,7 +4858,7 @@
         <v>21</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>12</v>
+        <v>110</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
@@ -4860,7 +4878,7 @@
         <v>24</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>12</v>
+        <v>107</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
@@ -4880,7 +4898,7 @@
         <v>27</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>5</v>
+        <v>34</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
@@ -4900,7 +4918,7 @@
         <v>30</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
@@ -4914,30 +4932,30 @@
         <v>3</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>350</v>
+        <v>100</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="B165" s="1" t="s">
         <v>351</v>
       </c>
-      <c r="B165" s="1" t="s">
+      <c r="C165" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D165" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="C165" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D165" s="1" t="s">
-        <v>350</v>
-      </c>
       <c r="E165" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F165" s="1" t="s">
         <v>34</v>
@@ -4954,10 +4972,10 @@
         <v>3</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F166" s="1" t="s">
         <v>34</v>
@@ -4974,10 +4992,10 @@
         <v>3</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F167" s="1" t="s">
         <v>34</v>
@@ -4994,10 +5012,10 @@
         <v>3</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F168" s="1" t="s">
         <v>34</v>
@@ -5014,13 +5032,13 @@
         <v>3</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>107</v>
+        <v>34</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
@@ -5034,33 +5052,33 @@
         <v>3</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>363</v>
+        <v>352</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>12</v>
+        <v>107</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="B171" s="1" t="s">
         <v>364</v>
       </c>
-      <c r="B171" s="1" t="s">
+      <c r="C171" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D171" s="1" t="s">
         <v>365</v>
       </c>
-      <c r="C171" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D171" s="1" t="s">
-        <v>363</v>
-      </c>
       <c r="E171" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
@@ -5074,33 +5092,33 @@
         <v>3</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>368</v>
+        <v>34</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="B173" s="1" t="s">
         <v>369</v>
       </c>
-      <c r="B173" s="1" t="s">
+      <c r="C173" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D173" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="E173" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F173" s="1" t="s">
         <v>370</v>
-      </c>
-      <c r="C173" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D173" s="1" t="s">
-        <v>363</v>
-      </c>
-      <c r="E173" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F173" s="1" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
@@ -5114,50 +5132,50 @@
         <v>3</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F174" s="1" t="s">
-        <v>34</v>
+        <v>110</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="B175" s="1" t="s">
         <v>374</v>
       </c>
-      <c r="B175" s="1" t="s">
+      <c r="C175" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D175" s="1" t="s">
         <v>375</v>
-      </c>
-      <c r="C175" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D175" s="1" t="s">
-        <v>376</v>
       </c>
       <c r="E175" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="B176" s="1" t="s">
         <v>377</v>
       </c>
-      <c r="B176" s="1" t="s">
-        <v>378</v>
-      </c>
       <c r="C176" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F176" s="1" t="s">
         <v>34</v>
@@ -5165,59 +5183,59 @@
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="B177" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="C177" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D177" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="B177" s="1" t="s">
-        <v>381</v>
-      </c>
-      <c r="C177" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D177" s="1" t="s">
-        <v>379</v>
-      </c>
       <c r="E177" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>107</v>
+        <v>12</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="B178" s="1" t="s">
         <v>382</v>
       </c>
-      <c r="B178" s="1" t="s">
-        <v>383</v>
-      </c>
       <c r="C178" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>368</v>
+        <v>34</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="B179" s="1" t="s">
         <v>384</v>
       </c>
-      <c r="B179" s="1" t="s">
+      <c r="C179" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D179" s="1" t="s">
         <v>385</v>
       </c>
-      <c r="C179" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D179" s="1" t="s">
-        <v>379</v>
-      </c>
       <c r="E179" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F179" s="1" t="s">
         <v>34</v>
@@ -5234,13 +5252,13 @@
         <v>3</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>34</v>
+        <v>107</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
@@ -5254,173 +5272,233 @@
         <v>3</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F181" s="1" t="s">
-        <v>12</v>
+        <v>370</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="B182" s="1" t="s">
         <v>391</v>
       </c>
-      <c r="B182" s="1" t="s">
-        <v>392</v>
-      </c>
       <c r="C182" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F182" s="1" t="s">
-        <v>393</v>
+        <v>34</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="C183" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F183" s="1" t="s">
-        <v>396</v>
+        <v>34</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="C184" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F184" s="1" t="s">
-        <v>399</v>
+        <v>110</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="C185" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>390</v>
+        <v>398</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F185" s="1" t="s">
-        <v>396</v>
+        <v>5</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="C186" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>390</v>
+        <v>398</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F186" s="1" t="s">
-        <v>110</v>
+        <v>5</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="C187" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>390</v>
+        <v>398</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="F187" s="1" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="C188" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>390</v>
+        <v>398</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="F188" s="1" t="s">
-        <v>110</v>
+        <v>405</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="B189" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="C189" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D189" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="E189" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F189" s="1" t="s">
         <v>408</v>
       </c>
-      <c r="B189" s="1" t="s">
+    </row>
+    <row r="190" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A190" s="1" t="s">
         <v>409</v>
       </c>
-      <c r="C189" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D189" s="1" t="s">
-        <v>390</v>
-      </c>
-      <c r="E189" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F189" s="1" t="s">
-        <v>34</v>
+      <c r="B190" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="C190" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D190" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="E190" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F190" s="1" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="191" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A191" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="B191" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="C191" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D191" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="E191" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F191" s="1" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="192" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A192" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="B192" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="C192" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D192" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="E192" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F192" s="1" t="s">
+        <v>110</v>
       </c>
     </row>
   </sheetData>
